--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127277553</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127277701</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127278308</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,29 +1119,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,32 +1226,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1269,7 +1256,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,24 +1333,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1442,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,24 +1445,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>78678</v>
+        <v>91345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440731</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277819</v>
+        <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440731</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>6763206</v>
+        <v>6763098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277907</v>
       </c>
       <c r="B17" t="n">
-        <v>91339</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440726</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763215</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,22 +2398,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278078</v>
+        <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,39 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440780</v>
+        <v>440871</v>
       </c>
       <c r="R18" t="n">
-        <v>6763258</v>
+        <v>6763370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278318</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440871</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763370</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R24" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,22 +3152,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R25" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4145,7 +4145,7 @@
         <v>127276706</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127276652</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,39 +4367,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440585</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763104</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,45 +4463,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127278026</v>
+        <v>127276652</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440756</v>
+        <v>440585</v>
       </c>
       <c r="R37" t="n">
-        <v>6763227</v>
+        <v>6763104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127277966</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,39 +4800,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440736</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763240</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4981,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,22 +4991,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5039,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,22 +5098,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,34 +5121,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R43" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277553</v>
+        <v>127278308</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440681</v>
+        <v>440880</v>
       </c>
       <c r="R3" t="n">
-        <v>6763167</v>
+        <v>6763342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277701</v>
+        <v>127277553</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440706</v>
+        <v>440681</v>
       </c>
       <c r="R4" t="n">
-        <v>6763216</v>
+        <v>6763167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127277701</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440706</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>91345</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,12 +2077,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B16" t="n">
         <v>91345</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277907</v>
+        <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>91345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440726</v>
+        <v>440591</v>
       </c>
       <c r="R17" t="n">
-        <v>6763215</v>
+        <v>6763079</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,7 +3816,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278126</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3842,17 +3847,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,42 +3934,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127278264</v>
+        <v>127276706</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,39 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440865</v>
+        <v>440618</v>
       </c>
       <c r="R33" t="n">
-        <v>6763319</v>
+        <v>6763089</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,7 +4137,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127276706</v>
+        <v>127277376</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4177,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440618</v>
+        <v>440671</v>
       </c>
       <c r="R34" t="n">
-        <v>6763089</v>
+        <v>6763153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127277376</v>
+        <v>127278264</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,34 +4255,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440671</v>
+        <v>440865</v>
       </c>
       <c r="R35" t="n">
-        <v>6763153</v>
+        <v>6763319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278193</v>
+        <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440832</v>
+        <v>440681</v>
       </c>
       <c r="R2" t="n">
-        <v>6763295</v>
+        <v>6763167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127278308</v>
+        <v>127277701</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440880</v>
+        <v>440706</v>
       </c>
       <c r="R3" t="n">
-        <v>6763342</v>
+        <v>6763216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277553</v>
+        <v>127278193</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440681</v>
+        <v>440832</v>
       </c>
       <c r="R4" t="n">
-        <v>6763167</v>
+        <v>6763295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R5" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277553</v>
+        <v>127277701</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440681</v>
+        <v>440706</v>
       </c>
       <c r="R2" t="n">
-        <v>6763167</v>
+        <v>6763216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R3" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127277553</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440681</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,24 +1119,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,24 +1231,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1256,7 +1269,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,29 +1346,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1434,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,32 +1453,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276757</v>
+        <v>127277819</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440731</v>
       </c>
       <c r="R15" t="n">
-        <v>6763098</v>
+        <v>6763206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127277819</v>
+        <v>127276757</v>
       </c>
       <c r="B16" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440731</v>
+        <v>440624</v>
       </c>
       <c r="R16" t="n">
-        <v>6763206</v>
+        <v>6763098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
         <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278318</v>
+        <v>127278078</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2421,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440871</v>
+        <v>440780</v>
       </c>
       <c r="R18" t="n">
-        <v>6763370</v>
+        <v>6763258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127278318</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2552,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440871</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,39 +2640,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278104</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,34 +3822,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127276706</v>
+        <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4041,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440618</v>
+        <v>440865</v>
       </c>
       <c r="R33" t="n">
-        <v>6763089</v>
+        <v>6763319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,7 +4142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127277376</v>
+        <v>127276706</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440671</v>
+        <v>440618</v>
       </c>
       <c r="R34" t="n">
-        <v>6763153</v>
+        <v>6763089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,10 +4249,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127278264</v>
+        <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,39 +4260,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440865</v>
+        <v>440671</v>
       </c>
       <c r="R35" t="n">
-        <v>6763319</v>
+        <v>6763153</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127277966</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,34 +4800,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440736</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4901,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127278152</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4927,17 +4932,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440813</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763291</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4971,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4981,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,19 +4996,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -5034,17 +5039,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5078,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5088,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,22 +5103,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277966</v>
+        <v>127276679</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,39 +5126,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440736</v>
+        <v>440602</v>
       </c>
       <c r="R43" t="n">
-        <v>6763240</v>
+        <v>6763069</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127278264</v>
+        <v>127276706</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,39 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440865</v>
+        <v>440618</v>
       </c>
       <c r="R33" t="n">
-        <v>6763319</v>
+        <v>6763089</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,7 +4137,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127276706</v>
+        <v>127277376</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4177,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440618</v>
+        <v>440671</v>
       </c>
       <c r="R34" t="n">
-        <v>6763089</v>
+        <v>6763153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127277376</v>
+        <v>127278264</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,34 +4255,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440671</v>
+        <v>440865</v>
       </c>
       <c r="R35" t="n">
-        <v>6763153</v>
+        <v>6763319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277701</v>
+        <v>127277553</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440706</v>
+        <v>440681</v>
       </c>
       <c r="R2" t="n">
-        <v>6763216</v>
+        <v>6763167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127278308</v>
+        <v>127277701</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440880</v>
+        <v>440706</v>
       </c>
       <c r="R3" t="n">
-        <v>6763342</v>
+        <v>6763216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278193</v>
+        <v>127278308</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440832</v>
+        <v>440880</v>
       </c>
       <c r="R4" t="n">
-        <v>6763295</v>
+        <v>6763342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127277553</v>
+        <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440681</v>
+        <v>440832</v>
       </c>
       <c r="R5" t="n">
-        <v>6763167</v>
+        <v>6763295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,29 +1119,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,32 +1226,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1269,7 +1256,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,24 +1333,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1442,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,24 +1445,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>91346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440731</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277819</v>
+        <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440731</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>6763206</v>
+        <v>6763098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277907</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440726</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763215</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278104</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3822,39 +3827,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127277966</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,39 +4800,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440736</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763240</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4932,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4981,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,19 +4991,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -5039,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,22 +5098,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,34 +5121,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R43" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278078</v>
+        <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,39 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440780</v>
+        <v>440871</v>
       </c>
       <c r="R18" t="n">
-        <v>6763258</v>
+        <v>6763370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278318</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2557,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440871</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763370</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,7 +3811,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3847,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,7 +3816,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278126</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3842,17 +3847,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,42 +3934,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127277701</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127278308</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>91346</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,12 +2077,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
         <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277907</v>
+        <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440726</v>
+        <v>440591</v>
       </c>
       <c r="R17" t="n">
-        <v>6763215</v>
+        <v>6763079</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,22 +2398,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278318</v>
+        <v>127278078</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2421,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440871</v>
+        <v>440780</v>
       </c>
       <c r="R18" t="n">
-        <v>6763370</v>
+        <v>6763258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127278318</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440871</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,39 +2640,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
         <v>127276706</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>127277376</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>127278264</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,50 +4463,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127276652</v>
+        <v>127278026</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440585</v>
+        <v>440756</v>
       </c>
       <c r="R37" t="n">
-        <v>6763104</v>
+        <v>6763227</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,45 +4570,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127276652</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440585</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763104</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127277966</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,34 +4800,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440736</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127278152</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,17 +4932,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440813</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763291</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4971,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4981,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4996,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,17 +5039,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5078,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5088,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,22 +5103,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277966</v>
+        <v>127276679</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,39 +5126,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440736</v>
+        <v>440602</v>
       </c>
       <c r="R43" t="n">
-        <v>6763240</v>
+        <v>6763069</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277553</v>
+        <v>127278308</v>
       </c>
       <c r="B2" t="n">
         <v>79018</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440681</v>
+        <v>440880</v>
       </c>
       <c r="R2" t="n">
-        <v>6763167</v>
+        <v>6763342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277701</v>
+        <v>127277553</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440706</v>
+        <v>440681</v>
       </c>
       <c r="R3" t="n">
-        <v>6763216</v>
+        <v>6763167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278308</v>
+        <v>127277701</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440880</v>
+        <v>440706</v>
       </c>
       <c r="R4" t="n">
-        <v>6763342</v>
+        <v>6763216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278078</v>
+        <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,39 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440780</v>
+        <v>440871</v>
       </c>
       <c r="R18" t="n">
-        <v>6763258</v>
+        <v>6763370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278318</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2557,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440871</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763370</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R21" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R22" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R24" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,19 +3152,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R25" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R37" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127277966</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,39 +4800,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440736</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763240</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
         <v>79018</v>
@@ -4932,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4981,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,19 +4991,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -5039,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,22 +5098,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,34 +5121,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R43" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127278240</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1119,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R6" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,19 +1211,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127278357</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1246,14 +1254,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R7" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,22 +1318,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127278271</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1341,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R8" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,19 +1425,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127278349</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1463,27 +1466,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R9" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127276757</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440624</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763098</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276757</v>
+        <v>127277819</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440731</v>
       </c>
       <c r="R15" t="n">
-        <v>6763098</v>
+        <v>6763206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127277819</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
         <v>91350</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440731</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763206</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277907</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>78685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440726</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763215</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R21" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R22" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278240</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,45 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,19 +1203,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278357</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1254,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R7" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,22 +1310,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278271</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R8" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,19 +1422,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278349</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1466,24 +1463,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R9" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127276757</v>
+        <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440624</v>
+        <v>440731</v>
       </c>
       <c r="R14" t="n">
-        <v>6763098</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277819</v>
+        <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440731</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>6763206</v>
+        <v>6763098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R24" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,19 +3152,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R25" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4356,45 +4356,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127278026</v>
+        <v>127276652</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440756</v>
+        <v>440585</v>
       </c>
       <c r="R36" t="n">
-        <v>6763227</v>
+        <v>6763104</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,50 +4575,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127276652</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440585</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763104</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R2" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278193</v>
+        <v>127278308</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440832</v>
+        <v>440880</v>
       </c>
       <c r="R5" t="n">
-        <v>6763295</v>
+        <v>6763342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278193</v>
+        <v>127277701</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440832</v>
+        <v>440706</v>
       </c>
       <c r="R2" t="n">
-        <v>6763295</v>
+        <v>6763216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +785,7 @@
         <v>127277553</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R4" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127278271</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R6" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127278357</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R7" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>127277907</v>
       </c>
       <c r="B17" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,34 +2528,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,39 +2640,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R21" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R22" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278104</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,17 +3847,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,42 +3934,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127276706</v>
+        <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4041,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440618</v>
+        <v>440865</v>
       </c>
       <c r="R33" t="n">
-        <v>6763089</v>
+        <v>6763319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127277376</v>
+        <v>127276706</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440671</v>
+        <v>440618</v>
       </c>
       <c r="R34" t="n">
-        <v>6763153</v>
+        <v>6763089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,10 +4249,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127278264</v>
+        <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,39 +4260,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440865</v>
+        <v>440671</v>
       </c>
       <c r="R35" t="n">
-        <v>6763319</v>
+        <v>6763153</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,50 +4356,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127276652</v>
+        <v>127278026</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440585</v>
+        <v>440756</v>
       </c>
       <c r="R36" t="n">
-        <v>6763104</v>
+        <v>6763227</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127277073</v>
+        <v>127276652</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,34 +4474,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440635</v>
+        <v>440585</v>
       </c>
       <c r="R37" t="n">
-        <v>6763147</v>
+        <v>6763104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4991,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,12 +5098,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
         <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277701</v>
+        <v>127278193</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440706</v>
+        <v>440832</v>
       </c>
       <c r="R2" t="n">
-        <v>6763216</v>
+        <v>6763295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277553</v>
+        <v>127277701</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440681</v>
+        <v>440706</v>
       </c>
       <c r="R3" t="n">
-        <v>6763167</v>
+        <v>6763216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278308</v>
+        <v>127277553</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440880</v>
+        <v>440681</v>
       </c>
       <c r="R4" t="n">
-        <v>6763342</v>
+        <v>6763167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278193</v>
+        <v>127278308</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440832</v>
+        <v>440880</v>
       </c>
       <c r="R5" t="n">
-        <v>6763295</v>
+        <v>6763342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127277976</v>
+        <v>127278409</v>
       </c>
       <c r="B11" t="n">
         <v>79020</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440736</v>
+        <v>440845</v>
       </c>
       <c r="R11" t="n">
-        <v>6763240</v>
+        <v>6763347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127278409</v>
+        <v>127277976</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440845</v>
+        <v>440736</v>
       </c>
       <c r="R12" t="n">
-        <v>6763347</v>
+        <v>6763240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,12 +2077,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B16" t="n">
         <v>91352</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277907</v>
+        <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>78687</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440726</v>
+        <v>440591</v>
       </c>
       <c r="R17" t="n">
-        <v>6763215</v>
+        <v>6763079</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,39 +2528,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,7 +3811,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278104</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3847,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127278264</v>
+        <v>127277376</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,39 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440865</v>
+        <v>440671</v>
       </c>
       <c r="R33" t="n">
-        <v>6763319</v>
+        <v>6763153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4249,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127277376</v>
+        <v>127278264</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,34 +4255,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440671</v>
+        <v>440865</v>
       </c>
       <c r="R35" t="n">
-        <v>6763153</v>
+        <v>6763319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127276679</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440602</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127276679</v>
+        <v>127278152</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440602</v>
+        <v>440813</v>
       </c>
       <c r="R41" t="n">
-        <v>6763069</v>
+        <v>6763291</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127276652</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,34 +4367,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440585</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763104</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4468,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127276652</v>
+        <v>127277073</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,39 +4479,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440585</v>
+        <v>440635</v>
       </c>
       <c r="R37" t="n">
-        <v>6763104</v>
+        <v>6763147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278193</v>
+        <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440832</v>
+        <v>440681</v>
       </c>
       <c r="R2" t="n">
-        <v>6763295</v>
+        <v>6763167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277553</v>
+        <v>127278308</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440681</v>
+        <v>440880</v>
       </c>
       <c r="R4" t="n">
-        <v>6763167</v>
+        <v>6763342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278271</v>
+        <v>127278349</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278357</v>
+        <v>127278240</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1231,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R7" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,29 +1346,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1434,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,32 +1453,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127278409</v>
+        <v>127277976</v>
       </c>
       <c r="B11" t="n">
         <v>79020</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440845</v>
+        <v>440736</v>
       </c>
       <c r="R11" t="n">
-        <v>6763347</v>
+        <v>6763240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127277976</v>
+        <v>127278409</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440736</v>
+        <v>440845</v>
       </c>
       <c r="R12" t="n">
-        <v>6763240</v>
+        <v>6763347</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440731</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,12 +2077,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127277819</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
         <v>91352</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440731</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763206</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277907</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>78687</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440726</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763215</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R21" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R22" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127277376</v>
+        <v>127276706</v>
       </c>
       <c r="B33" t="n">
         <v>79020</v>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440671</v>
+        <v>440618</v>
       </c>
       <c r="R33" t="n">
-        <v>6763153</v>
+        <v>6763089</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127276706</v>
+        <v>127277376</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440618</v>
+        <v>440671</v>
       </c>
       <c r="R34" t="n">
-        <v>6763089</v>
+        <v>6763153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127276652</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,39 +4367,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440585</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763104</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127277073</v>
+        <v>127276652</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,34 +4474,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440635</v>
+        <v>440585</v>
       </c>
       <c r="R37" t="n">
-        <v>6763147</v>
+        <v>6763104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127276679</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440602</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763069</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4927,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,19 +4991,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
         <v>79020</v>
@@ -5034,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,12 +5098,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,29 +1119,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,32 +1226,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1269,7 +1256,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,24 +1333,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1442,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,24 +1445,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1985,7 +1985,7 @@
         <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127276652</v>
+        <v>127277073</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,39 +4474,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440585</v>
+        <v>440635</v>
       </c>
       <c r="R37" t="n">
-        <v>6763104</v>
+        <v>6763147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,45 +4570,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127276652</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440585</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763104</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4927,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,19 +4991,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
         <v>79020</v>
@@ -5034,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,12 +5098,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127277701</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127278308</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R15" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127277907</v>
       </c>
       <c r="B16" t="n">
-        <v>91358</v>
+        <v>78690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,37 +2207,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440726</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763215</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,22 +2291,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277907</v>
+        <v>127276757</v>
       </c>
       <c r="B17" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440726</v>
+        <v>440624</v>
       </c>
       <c r="R17" t="n">
-        <v>6763215</v>
+        <v>6763098</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
         <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>127277721</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278126</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,17 +3847,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,42 +3934,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127276706</v>
+        <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4041,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440618</v>
+        <v>440865</v>
       </c>
       <c r="R33" t="n">
-        <v>6763089</v>
+        <v>6763319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127277376</v>
+        <v>127276706</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440671</v>
+        <v>440618</v>
       </c>
       <c r="R34" t="n">
-        <v>6763153</v>
+        <v>6763089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,10 +4249,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127278264</v>
+        <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,39 +4260,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440865</v>
+        <v>440671</v>
       </c>
       <c r="R35" t="n">
-        <v>6763319</v>
+        <v>6763153</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R37" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>127276652</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4991,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,12 +5098,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
         <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R3" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R4" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278193</v>
+        <v>127277701</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440832</v>
+        <v>440706</v>
       </c>
       <c r="R5" t="n">
-        <v>6763295</v>
+        <v>6763216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
         <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B15" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R15" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127277907</v>
+        <v>127276757</v>
       </c>
       <c r="B16" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,37 +2207,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440726</v>
+        <v>440624</v>
       </c>
       <c r="R16" t="n">
-        <v>6763215</v>
+        <v>6763098</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,22 +2291,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>91369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,21 +2314,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R17" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
         <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>127277721</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278182</v>
+        <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,37 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440781</v>
+        <v>440630</v>
       </c>
       <c r="R21" t="n">
-        <v>6763260</v>
+        <v>6763107</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127276816</v>
+        <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440630</v>
+        <v>440781</v>
       </c>
       <c r="R22" t="n">
-        <v>6763107</v>
+        <v>6763260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278104</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,34 +3822,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3926,7 +3926,7 @@
         <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127278264</v>
+        <v>127276706</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,39 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440865</v>
+        <v>440618</v>
       </c>
       <c r="R33" t="n">
-        <v>6763319</v>
+        <v>6763089</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127276706</v>
+        <v>127277376</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440618</v>
+        <v>440671</v>
       </c>
       <c r="R34" t="n">
-        <v>6763089</v>
+        <v>6763153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127277376</v>
+        <v>127278264</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,34 +4255,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440671</v>
+        <v>440865</v>
       </c>
       <c r="R35" t="n">
-        <v>6763153</v>
+        <v>6763319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R37" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>127276652</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4991,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,34 +5014,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,10 +5115,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277966</v>
+        <v>127277514</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,42 +5126,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440736</v>
+        <v>440678</v>
       </c>
       <c r="R43" t="n">
-        <v>6763240</v>
+        <v>6763157</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5210,12 +5210,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277553</v>
+        <v>127278193</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440681</v>
+        <v>440832</v>
       </c>
       <c r="R2" t="n">
-        <v>6763167</v>
+        <v>6763295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127278308</v>
+        <v>127277553</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440880</v>
+        <v>440681</v>
       </c>
       <c r="R3" t="n">
-        <v>6763342</v>
+        <v>6763167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278193</v>
+        <v>127277701</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440832</v>
+        <v>440706</v>
       </c>
       <c r="R4" t="n">
-        <v>6763295</v>
+        <v>6763216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R5" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127278271</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1139,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R6" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127278349</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R7" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127278240</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1351,24 +1356,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R8" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1430,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127278357</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,45 +1453,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R9" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127277819</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440731</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>78696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,37 +2100,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R15" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
         <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278318</v>
+        <v>127278078</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2421,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440871</v>
+        <v>440780</v>
       </c>
       <c r="R18" t="n">
-        <v>6763370</v>
+        <v>6763258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127278318</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2552,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440871</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,39 +2640,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127277538</v>
+        <v>127278015</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440679</v>
+        <v>440758</v>
       </c>
       <c r="R23" t="n">
-        <v>6763165</v>
+        <v>6763237</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,19 +3045,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127277573</v>
+        <v>127277538</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440702</v>
+        <v>440679</v>
       </c>
       <c r="R24" t="n">
-        <v>6763178</v>
+        <v>6763165</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,7 +3164,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R25" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278104</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127276706</v>
+        <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4041,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440618</v>
+        <v>440865</v>
       </c>
       <c r="R33" t="n">
-        <v>6763089</v>
+        <v>6763319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,7 +4142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127277376</v>
+        <v>127276706</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440671</v>
+        <v>440618</v>
       </c>
       <c r="R34" t="n">
-        <v>6763153</v>
+        <v>6763089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,10 +4249,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127278264</v>
+        <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,39 +4260,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440865</v>
+        <v>440671</v>
       </c>
       <c r="R35" t="n">
-        <v>6763319</v>
+        <v>6763153</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127277073</v>
+        <v>127276652</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,34 +4474,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440635</v>
+        <v>440585</v>
       </c>
       <c r="R37" t="n">
-        <v>6763147</v>
+        <v>6763104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,50 +4575,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127276652</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440585</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763104</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127277966</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,34 +4800,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440736</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4901,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127276679</v>
+        <v>127278152</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440602</v>
+        <v>440813</v>
       </c>
       <c r="R41" t="n">
-        <v>6763069</v>
+        <v>6763291</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,10 +5008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277966</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,42 +5019,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440736</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763240</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,19 +5103,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5146,17 +5146,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R43" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5210,12 +5210,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278193</v>
+        <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440832</v>
+        <v>440681</v>
       </c>
       <c r="R2" t="n">
-        <v>6763295</v>
+        <v>6763167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277553</v>
+        <v>127277701</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440681</v>
+        <v>440706</v>
       </c>
       <c r="R3" t="n">
-        <v>6763167</v>
+        <v>6763216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R4" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278271</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1139,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278349</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R7" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,19 +1310,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278240</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1356,27 +1351,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440811</v>
+        <v>440872</v>
       </c>
       <c r="R8" t="n">
-        <v>6763283</v>
+        <v>6763382</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278357</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,37 +1445,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440872</v>
+        <v>440811</v>
       </c>
       <c r="R9" t="n">
-        <v>6763382</v>
+        <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277819</v>
+        <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,37 +1993,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440731</v>
+        <v>440726</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763215</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277907</v>
+        <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,37 +2100,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440726</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>6763215</v>
+        <v>6763098</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,22 +2184,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B17" t="n">
         <v>91370</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278078</v>
+        <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,39 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440780</v>
+        <v>440871</v>
       </c>
       <c r="R18" t="n">
-        <v>6763258</v>
+        <v>6763370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278318</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2557,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440871</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763370</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127278015</v>
+        <v>127277538</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440758</v>
+        <v>440679</v>
       </c>
       <c r="R23" t="n">
-        <v>6763237</v>
+        <v>6763165</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,19 +3045,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127277538</v>
+        <v>127277573</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440679</v>
+        <v>440702</v>
       </c>
       <c r="R24" t="n">
-        <v>6763165</v>
+        <v>6763178</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,7 +3164,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R25" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3822,42 +3822,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127277966</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,39 +4800,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440736</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763240</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4932,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4981,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,19 +4991,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -5039,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,22 +5098,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,34 +5121,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R43" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277553</v>
+        <v>127278193</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440681</v>
+        <v>440832</v>
       </c>
       <c r="R2" t="n">
-        <v>6763167</v>
+        <v>6763295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277701</v>
+        <v>127277553</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440706</v>
+        <v>440681</v>
       </c>
       <c r="R3" t="n">
-        <v>6763216</v>
+        <v>6763167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278308</v>
+        <v>127277701</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440880</v>
+        <v>440706</v>
       </c>
       <c r="R4" t="n">
-        <v>6763342</v>
+        <v>6763216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278193</v>
+        <v>127278308</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440832</v>
+        <v>440880</v>
       </c>
       <c r="R5" t="n">
-        <v>6763295</v>
+        <v>6763342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,24 +1119,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,24 +1231,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1256,7 +1269,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,29 +1346,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1434,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,32 +1453,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276757</v>
+        <v>127277819</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>91339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440731</v>
       </c>
       <c r="R15" t="n">
-        <v>6763098</v>
+        <v>6763206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127276757</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440624</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277819</v>
+        <v>127276666</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440731</v>
+        <v>440591</v>
       </c>
       <c r="R17" t="n">
-        <v>6763206</v>
+        <v>6763079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278318</v>
+        <v>127278078</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2421,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440871</v>
+        <v>440780</v>
       </c>
       <c r="R18" t="n">
-        <v>6763370</v>
+        <v>6763258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127278318</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440871</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277721</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,39 +2640,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440731</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R24" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,22 +3152,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R25" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278021</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440756</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278126</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,17 +3847,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440785</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763269</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127277590</v>
       </c>
       <c r="B32" t="n">
-        <v>57669</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,42 +3934,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440698</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
         <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127276706</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127276652</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,34 +4367,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440585</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763104</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,50 +4468,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127276652</v>
+        <v>127278026</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>8447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440585</v>
+        <v>440756</v>
       </c>
       <c r="R37" t="n">
-        <v>6763104</v>
+        <v>6763227</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127277073</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440635</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763147</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127277966</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,34 +4800,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440736</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127278152</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,17 +4932,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440813</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763291</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4971,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4981,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4996,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127277514</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,17 +5039,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440678</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763157</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5073,7 +5078,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5088,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,22 +5103,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277966</v>
+        <v>127276679</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,39 +5126,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440736</v>
+        <v>440602</v>
       </c>
       <c r="R43" t="n">
-        <v>6763240</v>
+        <v>6763069</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127278193</v>
+        <v>127277553</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440832</v>
+        <v>440681</v>
       </c>
       <c r="R2" t="n">
-        <v>6763295</v>
+        <v>6763167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277553</v>
+        <v>127277701</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440681</v>
+        <v>440706</v>
       </c>
       <c r="R3" t="n">
-        <v>6763167</v>
+        <v>6763216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127277701</v>
+        <v>127278308</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440706</v>
+        <v>440880</v>
       </c>
       <c r="R4" t="n">
-        <v>6763216</v>
+        <v>6763342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278308</v>
+        <v>127278193</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440880</v>
+        <v>440832</v>
       </c>
       <c r="R5" t="n">
-        <v>6763342</v>
+        <v>6763295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278349</v>
+        <v>127278357</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,29 +1119,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278240</v>
+        <v>127278271</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,32 +1226,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1269,7 +1256,7 @@
         <v>6763283</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278357</v>
+        <v>127278349</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,24 +1333,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -1442,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278271</v>
+        <v>127278240</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,24 +1445,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
@@ -1483,7 +1483,7 @@
         <v>6763283</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,7 +1552,7 @@
         <v>127277674</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>127277976</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>127278409</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127276835</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127277907</v>
       </c>
       <c r="B14" t="n">
-        <v>78678</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127277819</v>
+        <v>127276757</v>
       </c>
       <c r="B15" t="n">
-        <v>91339</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440731</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>6763206</v>
+        <v>6763098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276757</v>
+        <v>127276666</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440624</v>
+        <v>440591</v>
       </c>
       <c r="R16" t="n">
-        <v>6763098</v>
+        <v>6763079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127276666</v>
+        <v>127277819</v>
       </c>
       <c r="B17" t="n">
-        <v>91339</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440591</v>
+        <v>440731</v>
       </c>
       <c r="R17" t="n">
-        <v>6763079</v>
+        <v>6763206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278078</v>
+        <v>127278318</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,39 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440780</v>
+        <v>440871</v>
       </c>
       <c r="R18" t="n">
-        <v>6763258</v>
+        <v>6763370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127278318</v>
+        <v>127277721</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440871</v>
+        <v>440731</v>
       </c>
       <c r="R19" t="n">
-        <v>6763370</v>
+        <v>6763206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127277721</v>
+        <v>127278078</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440731</v>
+        <v>440780</v>
       </c>
       <c r="R20" t="n">
-        <v>6763206</v>
+        <v>6763258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>127276816</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>127278182</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127277538</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127278015</v>
+        <v>127277573</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440758</v>
+        <v>440702</v>
       </c>
       <c r="R24" t="n">
-        <v>6763237</v>
+        <v>6763178</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,22 +3152,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127277573</v>
+        <v>127278015</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440702</v>
+        <v>440758</v>
       </c>
       <c r="R25" t="n">
-        <v>6763178</v>
+        <v>6763237</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>127277093</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>127277534</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>127278224</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>127276668</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278021</v>
+        <v>127278126</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,39 +3715,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440756</v>
+        <v>440785</v>
       </c>
       <c r="R30" t="n">
-        <v>6763227</v>
+        <v>6763269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127278126</v>
+        <v>127277590</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440785</v>
+        <v>440698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763269</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3906,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127277590</v>
+        <v>127278021</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,37 +3929,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440698</v>
+        <v>440756</v>
       </c>
       <c r="R32" t="n">
-        <v>6763171</v>
+        <v>6763227</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
         <v>127278264</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127276706</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>127277376</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127276652</v>
+        <v>127277073</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,39 +4367,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440585</v>
+        <v>440635</v>
       </c>
       <c r="R36" t="n">
-        <v>6763104</v>
+        <v>6763147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,45 +4463,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127278026</v>
+        <v>127276652</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440756</v>
+        <v>440585</v>
       </c>
       <c r="R37" t="n">
-        <v>6763227</v>
+        <v>6763104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127277073</v>
+        <v>127278026</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440635</v>
+        <v>440756</v>
       </c>
       <c r="R38" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
         <v>127278274</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127277966</v>
+        <v>127278152</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,39 +4800,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440736</v>
+        <v>440813</v>
       </c>
       <c r="R40" t="n">
-        <v>6763240</v>
+        <v>6763291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127278152</v>
+        <v>127277514</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,17 +4927,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440813</v>
+        <v>440678</v>
       </c>
       <c r="R41" t="n">
-        <v>6763291</v>
+        <v>6763157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4981,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,22 +4991,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127277514</v>
+        <v>127276679</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5039,17 +5034,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440678</v>
+        <v>440602</v>
       </c>
       <c r="R42" t="n">
-        <v>6763157</v>
+        <v>6763069</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,22 +5098,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127276679</v>
+        <v>127277966</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,34 +5121,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440602</v>
+        <v>440736</v>
       </c>
       <c r="R43" t="n">
-        <v>6763069</v>
+        <v>6763240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>127277030</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127277553</v>
+        <v>127277907</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440681</v>
+        <v>440726</v>
       </c>
       <c r="R2" t="n">
-        <v>6763167</v>
+        <v>6763215</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127277701</v>
+        <v>127276666</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440706</v>
+        <v>440591</v>
       </c>
       <c r="R3" t="n">
-        <v>6763216</v>
+        <v>6763079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127278308</v>
+        <v>127277819</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440880</v>
+        <v>440731</v>
       </c>
       <c r="R4" t="n">
-        <v>6763342</v>
+        <v>6763206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127278193</v>
+        <v>127276668</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440832</v>
+        <v>440591</v>
       </c>
       <c r="R5" t="n">
-        <v>6763295</v>
+        <v>6763079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127278357</v>
+        <v>127276679</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440602</v>
       </c>
       <c r="R6" t="n">
-        <v>6763382</v>
+        <v>6763069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127278271</v>
+        <v>127276706</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1246,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440811</v>
+        <v>440618</v>
       </c>
       <c r="R7" t="n">
-        <v>6763283</v>
+        <v>6763089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,62 +1305,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127278349</v>
+        <v>127276757</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440872</v>
+        <v>440624</v>
       </c>
       <c r="R8" t="n">
-        <v>6763382</v>
+        <v>6763098</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,56 +1424,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127278240</v>
+        <v>127276816</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440811</v>
+        <v>440630</v>
       </c>
       <c r="R9" t="n">
-        <v>6763283</v>
+        <v>6763107</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,26 +1519,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127277674</v>
+        <v>127277030</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1584,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440685</v>
+        <v>440654</v>
       </c>
       <c r="R10" t="n">
-        <v>6763179</v>
+        <v>6763147</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,26 +1626,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127277976</v>
+        <v>127277073</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1691,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440736</v>
+        <v>440635</v>
       </c>
       <c r="R11" t="n">
-        <v>6763240</v>
+        <v>6763147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127278409</v>
+        <v>127277376</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1798,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440845</v>
+        <v>440671</v>
       </c>
       <c r="R12" t="n">
-        <v>6763347</v>
+        <v>6763153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,53 +1852,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127276835</v>
+        <v>127277514</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440630</v>
+        <v>440678</v>
       </c>
       <c r="R13" t="n">
-        <v>6763107</v>
+        <v>6763157</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,44 +1947,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127277907</v>
+        <v>127277534</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440726</v>
+        <v>440679</v>
       </c>
       <c r="R14" t="n">
-        <v>6763215</v>
+        <v>6763152</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,26 +2054,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127276757</v>
+        <v>127277538</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2120,17 +2097,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440679</v>
       </c>
       <c r="R15" t="n">
-        <v>6763098</v>
+        <v>6763165</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,44 +2161,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127276666</v>
+        <v>127277553</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440591</v>
+        <v>440681</v>
       </c>
       <c r="R16" t="n">
-        <v>6763079</v>
+        <v>6763167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,48 +2280,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127277819</v>
+        <v>127277573</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440731</v>
+        <v>440702</v>
       </c>
       <c r="R17" t="n">
-        <v>6763206</v>
+        <v>6763178</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,26 +2375,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127278318</v>
+        <v>127277590</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2441,17 +2418,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440871</v>
+        <v>440698</v>
       </c>
       <c r="R18" t="n">
-        <v>6763370</v>
+        <v>6763171</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,26 +2482,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127277721</v>
+        <v>127277674</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2548,17 +2525,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440731</v>
+        <v>440685</v>
       </c>
       <c r="R19" t="n">
-        <v>6763206</v>
+        <v>6763179</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,62 +2589,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127278078</v>
+        <v>127277661</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440780</v>
+        <v>440706</v>
       </c>
       <c r="R20" t="n">
-        <v>6763258</v>
+        <v>6763216</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127276816</v>
+        <v>127277721</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2771,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440630</v>
+        <v>440731</v>
       </c>
       <c r="R21" t="n">
-        <v>6763107</v>
+        <v>6763206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,48 +2815,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278182</v>
+        <v>127277976</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440781</v>
+        <v>440736</v>
       </c>
       <c r="R22" t="n">
-        <v>6763260</v>
+        <v>6763240</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,26 +2910,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127277538</v>
+        <v>127278015</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2985,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440679</v>
+        <v>440758</v>
       </c>
       <c r="R23" t="n">
-        <v>6763165</v>
+        <v>6763237</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3020,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,26 +3017,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127277573</v>
+        <v>127278104</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3088,17 +3060,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440702</v>
+        <v>440785</v>
       </c>
       <c r="R24" t="n">
-        <v>6763178</v>
+        <v>6763269</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3127,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,26 +3124,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127278015</v>
+        <v>127278152</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3195,17 +3167,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440758</v>
+        <v>440813</v>
       </c>
       <c r="R25" t="n">
-        <v>6763237</v>
+        <v>6763291</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3234,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,62 +3231,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127277093</v>
+        <v>127278211</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440653</v>
+        <v>440832</v>
       </c>
       <c r="R26" t="n">
-        <v>6763162</v>
+        <v>6763295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,14 +3350,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127277534</v>
+        <v>127278271</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3418,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440679</v>
+        <v>440811</v>
       </c>
       <c r="R27" t="n">
-        <v>6763152</v>
+        <v>6763283</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3453,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3463,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3490,14 +3457,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127278224</v>
+        <v>127278274</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3525,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440832</v>
+        <v>440865</v>
       </c>
       <c r="R28" t="n">
-        <v>6763295</v>
+        <v>6763319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3597,14 +3564,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127276668</v>
+        <v>127278285</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3632,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440591</v>
+        <v>440880</v>
       </c>
       <c r="R29" t="n">
-        <v>6763079</v>
+        <v>6763342</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3704,14 +3671,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127278126</v>
+        <v>127278318</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3739,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440785</v>
+        <v>440871</v>
       </c>
       <c r="R30" t="n">
-        <v>6763269</v>
+        <v>6763370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,14 +3778,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277590</v>
+        <v>127278330</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3842,17 +3809,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440698</v>
+        <v>440872</v>
       </c>
       <c r="R31" t="n">
-        <v>6763171</v>
+        <v>6763382</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3881,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3891,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,62 +3873,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127278021</v>
+        <v>127278409</v>
       </c>
       <c r="B32" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440756</v>
+        <v>440845</v>
       </c>
       <c r="R32" t="n">
-        <v>6763227</v>
+        <v>6763347</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4030,27 +3992,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127278264</v>
+        <v>127278021</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4061,7 +4023,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4070,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440865</v>
+        <v>440756</v>
       </c>
       <c r="R33" t="n">
-        <v>6763319</v>
+        <v>6763227</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,48 +4104,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127276706</v>
+        <v>127278182</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440618</v>
+        <v>440781</v>
       </c>
       <c r="R34" t="n">
-        <v>6763089</v>
+        <v>6763260</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4212,7 +4174,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4222,7 +4184,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,22 +4199,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127277376</v>
+        <v>127276652</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,34 +4222,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440671</v>
+        <v>440585</v>
       </c>
       <c r="R35" t="n">
-        <v>6763153</v>
+        <v>6763104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,10 +4323,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127277073</v>
+        <v>127276835</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,34 +4334,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440635</v>
+        <v>440630</v>
       </c>
       <c r="R36" t="n">
-        <v>6763147</v>
+        <v>6763107</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127276652</v>
+        <v>127277093</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440585</v>
+        <v>440653</v>
       </c>
       <c r="R37" t="n">
-        <v>6763104</v>
+        <v>6763162</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,45 +4547,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127278026</v>
+        <v>127277966</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440756</v>
+        <v>440736</v>
       </c>
       <c r="R38" t="n">
-        <v>6763227</v>
+        <v>6763240</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127278274</v>
+        <v>127278078</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,34 +4670,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440865</v>
+        <v>440780</v>
       </c>
       <c r="R39" t="n">
-        <v>6763319</v>
+        <v>6763258</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127278152</v>
+        <v>127278193</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,34 +4782,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440813</v>
+        <v>440832</v>
       </c>
       <c r="R40" t="n">
-        <v>6763291</v>
+        <v>6763295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127277514</v>
+        <v>127278240</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,37 +4894,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440678</v>
+        <v>440811</v>
       </c>
       <c r="R41" t="n">
-        <v>6763157</v>
+        <v>6763283</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,22 +4986,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127276679</v>
+        <v>127278264</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,34 +5009,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440602</v>
+        <v>440865</v>
       </c>
       <c r="R42" t="n">
-        <v>6763069</v>
+        <v>6763319</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127277966</v>
+        <v>127278349</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440736</v>
+        <v>440872</v>
       </c>
       <c r="R43" t="n">
-        <v>6763240</v>
+        <v>6763382</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5222,48 +5222,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127277030</v>
+        <v>127278026</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440654</v>
+        <v>440756</v>
       </c>
       <c r="R44" t="n">
-        <v>6763147</v>
+        <v>6763227</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,12 +5317,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 34719-2025 artfynd.xlsx
+++ b/artfynd/A 34719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277907</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276666</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276668</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276679</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276706</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276757</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276816</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277030</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277376</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277514</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277534</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277538</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277553</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277573</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277674</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277661</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277721</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277976</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278015</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278104</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278152</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278211</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278271</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278274</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278285</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278318</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278330</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278409</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278021</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4208,6 +4373,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278182</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4320,6 +4490,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276652</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4432,6 +4607,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276835</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4544,6 +4724,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277093</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4656,6 +4841,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127277966</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4768,6 +4958,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278078</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4880,6 +5075,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278193</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4995,6 +5195,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278240</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5107,6 +5312,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278264</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5219,6 +5429,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278349</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5326,8 +5541,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127278026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>